--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F94C8B-2FDD-44E5-A7A2-C895FC2FF055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E91B622-BC5C-402B-A52D-33DD62E0777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="15" windowWidth="15300" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5670" yWindow="570" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
   <si>
     <t>티커</t>
   </si>
@@ -244,12 +244,6 @@
     <t>신영증권</t>
   </si>
   <si>
-    <t>001290</t>
-  </si>
-  <si>
-    <t>상상인증권</t>
-  </si>
-  <si>
     <t>035760</t>
   </si>
   <si>
@@ -478,12 +472,6 @@
     <t>F&amp;F</t>
   </si>
   <si>
-    <t>011200</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
     <t>053210</t>
   </si>
   <si>
@@ -860,13 +848,382 @@
   </si>
   <si>
     <t>한전산업</t>
+  </si>
+  <si>
+    <t>섹터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스유틸리티</t>
+  </si>
+  <si>
+    <t>017940</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스유틸리티</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003480</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한진중공업홀딩스</t>
+  </si>
+  <si>
+    <t>016710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대성홀딩스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVENI</t>
+  </si>
+  <si>
+    <t>015360</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기유틸리티</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이어블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>065530</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신서비스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>082640</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동양생명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000400</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데손해보험</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>064820</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>001500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대차증권</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000680</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LS네트웍스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003530</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화투자증권</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>190650</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코리아에셋투자증권</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003460</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유화증권</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>088980</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맥쿼리인프라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>005430</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국공항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선광</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>095570</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AJ네트웍스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>044450</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KSS해운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>067900</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이엔텍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>012750</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>047050</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스코인터내셔널</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>001120</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LX인터내셔널</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>443060</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HD현대마린솔루션</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>017960</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국카본</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>082740</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화엔진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>017800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대엘리베이터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>034020</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>두산에너빌리티</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>105840</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>우진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>033100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제룡전기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>006260</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>008260</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NI스틸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>014280</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금강공업</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>018310</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼목에스폼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>047810</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국항공우주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>012450</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화에어로스페이스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>079550</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIG넥스원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>214430</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이쓰리시스템</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>009580</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무림P&amp;P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>081000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일진다이아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>004450</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼화왕관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>006120</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK디스커버리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>096770</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK이노베이션</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100090</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK오션플렌트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>044490</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태웅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,6 +1244,21 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF191F28"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -921,17 +1293,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1231,18 +1611,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1250,7 +1637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1282,7 +1669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1290,7 +1677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1298,7 +1685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1306,7 +1693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1314,7 +1701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1322,7 +1709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1330,7 +1717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1338,7 +1725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1346,7 +1733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1354,7 +1741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1490,7 +1877,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -1498,7 +1885,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -1506,7 +1893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1514,7 +1901,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1522,7 +1909,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -1530,7 +1917,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1538,7 +1925,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -1546,7 +1933,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -1554,7 +1941,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -1562,7 +1949,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -1570,7 +1957,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -1578,7 +1965,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -1586,7 +1973,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -1594,7 +1981,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1602,7 +1989,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -1610,31 +1997,40 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>94</v>
       </c>
       <c r="B48" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C48" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>96</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
       <c r="B50" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C50" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -1642,7 +2038,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -1650,7 +2046,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1658,7 +2054,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -1666,7 +2062,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -1674,7 +2070,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -1682,7 +2078,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -1690,7 +2086,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -1698,7 +2094,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -1706,7 +2102,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -1714,7 +2110,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -1722,7 +2118,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -1730,7 +2126,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -1738,7 +2134,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -2002,7 +2398,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -2010,47 +2406,62 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>194</v>
       </c>
       <c r="B98" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C98" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>196</v>
       </c>
       <c r="B99" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C99" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>198</v>
       </c>
       <c r="B100" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C100" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>200</v>
       </c>
       <c r="B101" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C101" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>202</v>
       </c>
       <c r="B102" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C102" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -2058,15 +2469,18 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>206</v>
       </c>
       <c r="B104" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C104" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -2074,7 +2488,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -2082,7 +2496,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -2090,7 +2504,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>214</v>
       </c>
@@ -2098,7 +2512,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -2106,7 +2520,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -2114,7 +2528,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>220</v>
       </c>
@@ -2122,7 +2536,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>222</v>
       </c>
@@ -2258,7 +2672,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>256</v>
       </c>
@@ -2266,7 +2680,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>258</v>
       </c>
@@ -2274,7 +2688,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>260</v>
       </c>
@@ -2282,7 +2696,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>262</v>
       </c>
@@ -2290,7 +2704,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>264</v>
       </c>
@@ -2298,7 +2712,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>266</v>
       </c>
@@ -2306,7 +2720,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>268</v>
       </c>
@@ -2314,48 +2728,422 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>270</v>
       </c>
       <c r="B136" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C136" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>272</v>
       </c>
       <c r="B137" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C137" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>274</v>
       </c>
       <c r="B138" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>276</v>
+      <c r="C138" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="B139" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>278</v>
-      </c>
-      <c r="B140" t="s">
         <v>279</v>
+      </c>
+      <c r="C139" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C140" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B141" t="s">
+        <v>284</v>
+      </c>
+      <c r="C141" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B144" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B145" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B146" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B147" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B148" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B149" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B150" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B151" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B152" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B153" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B154" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B155" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B156" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B157" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B158" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B159" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B160" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B161" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B162" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B163" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B164" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B165" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B166" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B167" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B168" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B169" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B170" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B171" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B172" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B174" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B175" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B176" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B178" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B179" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B180" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B181" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B182" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C48" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
+    <hyperlink ref="C104" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
+    <hyperlink ref="C99" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
+    <hyperlink ref="C101" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
+    <hyperlink ref="C100" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
+    <hyperlink ref="C102" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
+    <hyperlink ref="C98" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
+    <hyperlink ref="B142" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
+    <hyperlink ref="C50" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
+    <hyperlink ref="C138" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
+    <hyperlink ref="C136" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
+    <hyperlink ref="C137" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imho\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E91B622-BC5C-402B-A52D-33DD62E0777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ABEC03-FFD2-4527-8E93-815935ED9221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="570" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2790" yWindow="690" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="367">
   <si>
     <t>티커</t>
   </si>
@@ -296,12 +296,6 @@
   </si>
   <si>
     <t>한국경제TV</t>
-  </si>
-  <si>
-    <t>007460</t>
-  </si>
-  <si>
-    <t>에이프로젠</t>
   </si>
   <si>
     <t>036460</t>
@@ -1611,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -1626,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1996,6 +1990,9 @@
       <c r="B47" t="s">
         <v>93</v>
       </c>
+      <c r="C47" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -2004,8 +2001,8 @@
       <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>277</v>
+      <c r="C48" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2015,8 +2012,8 @@
       <c r="B49" t="s">
         <v>97</v>
       </c>
-      <c r="C49" t="s">
-        <v>287</v>
+      <c r="C49" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2026,9 +2023,6 @@
       <c r="B50" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>277</v>
-      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -2405,6 +2399,9 @@
       <c r="B97" t="s">
         <v>193</v>
       </c>
+      <c r="C97" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -2414,7 +2411,7 @@
         <v>195</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2425,7 +2422,7 @@
         <v>197</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -2436,7 +2433,7 @@
         <v>199</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -2447,7 +2444,7 @@
         <v>201</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -2457,9 +2454,6 @@
       <c r="B102" t="s">
         <v>203</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>277</v>
-      </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -2468,6 +2462,9 @@
       <c r="B103" t="s">
         <v>205</v>
       </c>
+      <c r="C103" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -2476,9 +2473,6 @@
       <c r="B104" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>277</v>
-      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -2727,6 +2721,9 @@
       <c r="B135" t="s">
         <v>269</v>
       </c>
+      <c r="C135" s="2" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -2736,7 +2733,7 @@
         <v>271</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2747,72 +2744,69 @@
         <v>273</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>274</v>
+      <c r="A138" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="B138" t="s">
-        <v>275</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>287</v>
+        <v>277</v>
+      </c>
+      <c r="C138" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C139" t="s">
         <v>278</v>
       </c>
-      <c r="B139" t="s">
-        <v>279</v>
-      </c>
-      <c r="C139" t="s">
-        <v>280</v>
-      </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" t="s">
         <v>282</v>
       </c>
       <c r="C140" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B141" t="s">
-        <v>284</v>
-      </c>
       <c r="C141" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C142" t="s">
-        <v>280</v>
+      <c r="C142" s="3" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C143" s="3" t="s">
+      <c r="B143" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2825,7 +2819,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
+      <c r="A145" s="4" t="s">
         <v>293</v>
       </c>
       <c r="B145" t="s">
@@ -2833,7 +2827,7 @@
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="3" t="s">
         <v>295</v>
       </c>
       <c r="B146" t="s">
@@ -3009,7 +3003,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="A168" s="4" t="s">
         <v>339</v>
       </c>
       <c r="B168" t="s">
@@ -3025,7 +3019,7 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="3" t="s">
         <v>343</v>
       </c>
       <c r="B170" t="s">
@@ -3120,29 +3114,21 @@
         <v>366</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B182" t="s">
-        <v>368</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C48" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
-    <hyperlink ref="C104" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
-    <hyperlink ref="C99" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
-    <hyperlink ref="C101" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
-    <hyperlink ref="C100" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
-    <hyperlink ref="C102" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
-    <hyperlink ref="C98" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
-    <hyperlink ref="B142" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
-    <hyperlink ref="C50" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
-    <hyperlink ref="C138" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
-    <hyperlink ref="C136" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
-    <hyperlink ref="C137" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
+    <hyperlink ref="C47" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
+    <hyperlink ref="C103" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
+    <hyperlink ref="C98" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
+    <hyperlink ref="C100" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
+    <hyperlink ref="C99" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
+    <hyperlink ref="C101" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
+    <hyperlink ref="C97" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
+    <hyperlink ref="B141" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
+    <hyperlink ref="C49" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
+    <hyperlink ref="C137" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
+    <hyperlink ref="C135" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
+    <hyperlink ref="C136" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ABEC03-FFD2-4527-8E93-815935ED9221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAA80C6-FA3A-4B7E-93E7-37678E9C73A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="690" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4575" yWindow="1530" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="385">
   <si>
     <t>티커</t>
   </si>
@@ -1210,6 +1210,74 @@
   </si>
   <si>
     <t>태웅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수산인더스트리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>126720</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>016250</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SGC E&amp;C</t>
+  </si>
+  <si>
+    <t>014530</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>극동유화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>012700</t>
+  </si>
+  <si>
+    <t>리드코프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>126880</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제이엔케이글로벌</t>
+  </si>
+  <si>
+    <t>대성산업</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKG휴켐스</t>
+  </si>
+  <si>
+    <t>007690</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국토화학</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>011780</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금호석유화학</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>069260</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>128820</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1217,7 +1285,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1253,6 +1321,25 @@
       <color rgb="FF191F28"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1291,7 +1378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1302,6 +1389,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1605,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -3112,6 +3217,78 @@
       </c>
       <c r="B181" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B184" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B185" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B187" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B188" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B189" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3131,5 +3308,6 @@
     <hyperlink ref="C136" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAA80C6-FA3A-4B7E-93E7-37678E9C73A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7574149D-C903-4B39-8C3B-DA88A200382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="1530" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="1755" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="393">
   <si>
     <t>티커</t>
   </si>
@@ -1278,6 +1278,33 @@
   </si>
   <si>
     <t>128820</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>004780</t>
+  </si>
+  <si>
+    <t>대륙제관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>004250</t>
+  </si>
+  <si>
+    <t>NPC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002200</t>
+  </si>
+  <si>
+    <t>한국수출포장</t>
+  </si>
+  <si>
+    <t>462520</t>
+  </si>
+  <si>
+    <t>조선내화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1710,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C194"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -3289,6 +3316,38 @@
       </c>
       <c r="B190" s="10" t="s">
         <v>378</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B191" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B192" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B194" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7574149D-C903-4B39-8C3B-DA88A200382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB79221-DB94-4853-940D-D193F1A542F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="1755" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1245" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="415">
   <si>
     <t>티커</t>
   </si>
@@ -1061,46 +1061,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>017800</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>현대엘리베이터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>034020</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>두산에너빌리티</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>105840</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>우진</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>033100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제룡전기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>006260</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>008260</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1130,22 +1090,6 @@
   </si>
   <si>
     <t>한국항공우주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>012450</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한화에어로스페이스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>079550</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIG넥스원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1305,6 +1249,184 @@
   </si>
   <si>
     <t>조선내화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000590</t>
+  </si>
+  <si>
+    <t>CS홀딩스</t>
+  </si>
+  <si>
+    <t>034810</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해성산업</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>079000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>와토스코리아</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>006570</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대림통상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000860</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>강남제비스코</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>066620</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국보디자인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002290</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>삼일기업공사</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>016800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍼시스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>028260</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>삼성물산</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003550</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LG </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>005440</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>현대지에프홀딩스</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이록코리아</t>
+  </si>
+  <si>
+    <t>049430</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코메론</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>092440</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기신정기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>013030</t>
+  </si>
+  <si>
+    <t>267250</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HD현대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101930</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인화정공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>086280</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대글로비스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>038390</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드캡투어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1312,7 +1434,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1368,6 +1490,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1377,7 +1505,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1400,12 +1528,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1433,6 +1581,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1737,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C194"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -3095,7 +3259,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
+      <c r="A163" s="4" t="s">
         <v>329</v>
       </c>
       <c r="B163" t="s">
@@ -3103,7 +3267,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+      <c r="A164" s="4" t="s">
         <v>331</v>
       </c>
       <c r="B164" t="s">
@@ -3135,7 +3299,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="3" t="s">
         <v>339</v>
       </c>
       <c r="B168" t="s">
@@ -3143,7 +3307,7 @@
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="3" t="s">
         <v>341</v>
       </c>
       <c r="B169" t="s">
@@ -3191,18 +3355,18 @@
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
+      <c r="A175" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B175" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B175" t="s">
-        <v>354</v>
-      </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+      <c r="A176" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="9" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3215,7 +3379,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
+      <c r="A178" s="10" t="s">
         <v>359</v>
       </c>
       <c r="B178" t="s">
@@ -3226,16 +3390,16 @@
       <c r="A179" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="10" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
+      <c r="A180" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="B180" t="s">
         <v>363</v>
-      </c>
-      <c r="B180" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
@@ -3247,23 +3411,23 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B182" t="s">
         <v>368</v>
       </c>
-      <c r="B182" s="6" t="s">
-        <v>367</v>
-      </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="8" t="s">
+      <c r="A183" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>370</v>
+      <c r="B183" s="10" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
+      <c r="A184" s="10" t="s">
         <v>371</v>
       </c>
       <c r="B184" t="s">
@@ -3279,7 +3443,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
+      <c r="A186" s="10" t="s">
         <v>375</v>
       </c>
       <c r="B186" s="10" t="s">
@@ -3287,23 +3451,23 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="11" t="s">
-        <v>384</v>
+      <c r="A187" s="10" t="s">
+        <v>377</v>
       </c>
       <c r="B187" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
+      <c r="A188" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="10" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="12" t="s">
         <v>381</v>
       </c>
       <c r="B189" t="s">
@@ -3311,15 +3475,15 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
+      <c r="A190" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B190" s="10" t="s">
-        <v>378</v>
+      <c r="B190" s="13" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="11" t="s">
         <v>385</v>
       </c>
       <c r="B191" t="s">
@@ -3327,18 +3491,18 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="10" t="s">
+      <c r="A192" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="10" t="s">
+      <c r="A193" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B193" t="s">
         <v>390</v>
       </c>
     </row>
@@ -3346,8 +3510,96 @@
       <c r="A194" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="15" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B195" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B196" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B197" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="B198" s="15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" s="17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="B202" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B203" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B204" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B205" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB79221-DB94-4853-940D-D193F1A542F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20FBDD-AEEF-4602-B337-1D804B63C741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1245" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="436">
   <si>
     <t>티커</t>
   </si>
@@ -1429,12 +1429,88 @@
     <t>레드캡투어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>065710</t>
+  </si>
+  <si>
+    <t>서호전기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>012330</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대모비스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200880</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서연이화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앤씨인터내셔널</t>
+  </si>
+  <si>
+    <t>352480</t>
+  </si>
+  <si>
+    <t>한국콜마</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000050</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경방</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영원무역홀딩스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>009970</t>
+  </si>
+  <si>
+    <t>051390</t>
+  </si>
+  <si>
+    <t>와이더블유</t>
+  </si>
+  <si>
+    <t>004590</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국가구</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>227840</t>
+  </si>
+  <si>
+    <t>현대코퍼레이션홀딩스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>001130</t>
+  </si>
+  <si>
+    <t>대한제분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1496,6 +1572,13 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1553,7 +1636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1582,20 +1665,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1901,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -3539,7 +3627,7 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="16" t="s">
+      <c r="A198" s="3" t="s">
         <v>399</v>
       </c>
       <c r="B198" s="15" t="s">
@@ -3547,7 +3635,7 @@
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="16" t="s">
+      <c r="A199" s="3" t="s">
         <v>402</v>
       </c>
       <c r="B199" t="s">
@@ -3555,10 +3643,10 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="16" t="s">
+      <c r="A200" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B200" s="17" t="s">
+      <c r="B200" s="16" t="s">
         <v>405</v>
       </c>
     </row>
@@ -3571,7 +3659,7 @@
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="16" t="s">
+      <c r="A202" s="3" t="s">
         <v>407</v>
       </c>
       <c r="B202" t="s">
@@ -3600,6 +3688,94 @@
       </c>
       <c r="B205" t="s">
         <v>414</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B206" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B207" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B208" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B210" s="17" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="B211" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B212" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B214" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="B215" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B216" s="17" t="s">
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20FBDD-AEEF-4602-B337-1D804B63C741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4BDE2-C2FB-400A-A9C9-767C3BFB4C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2010" yWindow="2145" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="426">
   <si>
     <t>티커</t>
   </si>
@@ -358,18 +358,6 @@
     <t>아세아시멘트</t>
   </si>
   <si>
-    <t>247540</t>
-  </si>
-  <si>
-    <t>에코프로비엠</t>
-  </si>
-  <si>
-    <t>048260</t>
-  </si>
-  <si>
-    <t>오스템임플란트</t>
-  </si>
-  <si>
     <t>084370</t>
   </si>
   <si>
@@ -430,12 +418,6 @@
     <t>에스앤에스텍</t>
   </si>
   <si>
-    <t>086520</t>
-  </si>
-  <si>
-    <t>에코프로</t>
-  </si>
-  <si>
     <t>003670</t>
   </si>
   <si>
@@ -448,22 +430,10 @@
     <t>한일시멘트</t>
   </si>
   <si>
-    <t>000120</t>
-  </si>
-  <si>
-    <t>CJ대한통운</t>
-  </si>
-  <si>
     <t>000990</t>
   </si>
   <si>
     <t>DB하이텍</t>
-  </si>
-  <si>
-    <t>383220</t>
-  </si>
-  <si>
-    <t>F&amp;F</t>
   </si>
   <si>
     <t>053210</t>
@@ -1636,7 +1606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1681,9 +1651,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1989,7 +1956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -2004,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2375,7 +2342,7 @@
         <v>93</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2386,7 +2353,7 @@
         <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2397,7 +2364,7 @@
         <v>97</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2648,7 +2615,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -2656,7 +2623,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -2664,7 +2631,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -2672,7 +2639,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>166</v>
       </c>
@@ -2680,7 +2647,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -2688,7 +2655,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -2696,7 +2663,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>172</v>
       </c>
@@ -2704,7 +2671,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>174</v>
       </c>
@@ -2712,7 +2679,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -2720,7 +2687,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -2728,7 +2695,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -2736,44 +2703,59 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>182</v>
       </c>
       <c r="B92" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C92" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>184</v>
       </c>
       <c r="B93" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C93" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>186</v>
       </c>
       <c r="B94" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C94" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>188</v>
       </c>
       <c r="B95" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C95" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>190</v>
       </c>
       <c r="B96" t="s">
         <v>191</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2783,9 +2765,6 @@
       <c r="B97" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -2795,7 +2774,7 @@
         <v>195</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2805,9 +2784,6 @@
       <c r="B99" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -2816,9 +2792,6 @@
       <c r="B100" t="s">
         <v>199</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -2827,9 +2800,6 @@
       <c r="B101" t="s">
         <v>201</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -2846,9 +2816,6 @@
       <c r="B103" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -3065,6 +3032,9 @@
       <c r="B130" t="s">
         <v>259</v>
       </c>
+      <c r="C130" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
@@ -3073,6 +3043,9 @@
       <c r="B131" t="s">
         <v>261</v>
       </c>
+      <c r="C131" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -3081,108 +3054,102 @@
       <c r="B132" t="s">
         <v>263</v>
       </c>
+      <c r="C132" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>264</v>
+      <c r="A133" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="B133" t="s">
-        <v>265</v>
+        <v>267</v>
+      </c>
+      <c r="C133" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>266</v>
-      </c>
-      <c r="B134" t="s">
-        <v>267</v>
+      <c r="A134" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C134" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135" t="s">
+        <v>272</v>
+      </c>
+      <c r="C135" t="s">
         <v>268</v>
       </c>
-      <c r="B135" t="s">
-        <v>269</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>285</v>
-      </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>270</v>
-      </c>
-      <c r="B136" t="s">
-        <v>271</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>285</v>
+      <c r="A136" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C136" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>272</v>
-      </c>
-      <c r="B137" t="s">
-        <v>273</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>285</v>
+      <c r="A137" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
-      </c>
-      <c r="C138" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C139" t="s">
-        <v>278</v>
+      <c r="A139" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B139" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
-        <v>281</v>
+      <c r="A140" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="B140" t="s">
-        <v>282</v>
-      </c>
-      <c r="C140" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C141" t="s">
-        <v>278</v>
+        <v>285</v>
+      </c>
+      <c r="B141" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C142" s="3" t="s">
+      <c r="B142" t="s">
         <v>288</v>
       </c>
     </row>
@@ -3203,7 +3170,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B145" t="s">
@@ -3307,7 +3274,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+      <c r="A158" s="4" t="s">
         <v>319</v>
       </c>
       <c r="B158" t="s">
@@ -3315,7 +3282,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+      <c r="A159" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B159" t="s">
@@ -3347,7 +3314,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="3" t="s">
         <v>329</v>
       </c>
       <c r="B163" t="s">
@@ -3355,7 +3322,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="3" t="s">
         <v>331</v>
       </c>
       <c r="B164" t="s">
@@ -3403,18 +3370,18 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="A170" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B170" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="B170" t="s">
-        <v>344</v>
-      </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
+      <c r="A171" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="9" t="s">
         <v>346</v>
       </c>
     </row>
@@ -3427,7 +3394,7 @@
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
+      <c r="A173" s="10" t="s">
         <v>349</v>
       </c>
       <c r="B173" t="s">
@@ -3438,28 +3405,28 @@
       <c r="A174" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="10" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B175" s="6" t="s">
+      <c r="A175" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B175" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B176" s="9" t="s">
+      <c r="B176" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
+      <c r="A177" s="11" t="s">
         <v>357</v>
       </c>
       <c r="B177" t="s">
@@ -3467,39 +3434,39 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="10" t="s">
+      <c r="A178" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B178" t="s">
-        <v>360</v>
+      <c r="B178" s="10" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
+      <c r="A179" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B179" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="11" t="s">
-        <v>370</v>
+      <c r="A180" s="10" t="s">
+        <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="10" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="10" t="s">
         <v>367</v>
       </c>
       <c r="B182" t="s">
@@ -3507,15 +3474,15 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
+      <c r="A183" s="10" t="s">
         <v>369</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="10" t="s">
+      <c r="A184" s="12" t="s">
         <v>371</v>
       </c>
       <c r="B184" t="s">
@@ -3526,47 +3493,47 @@
       <c r="A185" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="13" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="10" t="s">
+      <c r="A186" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="B186" s="10" t="s">
+      <c r="B186" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="15" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="10" t="s">
+      <c r="A188" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B188" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="12" t="s">
+      <c r="A189" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="15" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="10" t="s">
+      <c r="A190" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" t="s">
         <v>384</v>
       </c>
     </row>
@@ -3574,15 +3541,15 @@
       <c r="A191" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="15" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="14" t="s">
+      <c r="A192" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B192" s="15" t="s">
+      <c r="B192" t="s">
         <v>388</v>
       </c>
     </row>
@@ -3590,32 +3557,32 @@
       <c r="A193" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="15" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B194" s="15" t="s">
+      <c r="A194" s="3" t="s">
         <v>392</v>
+      </c>
+      <c r="B194" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B195" t="s">
         <v>394</v>
       </c>
+      <c r="B195" s="16" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="B196" s="15" t="s">
+      <c r="A196" s="10" t="s">
         <v>396</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
@@ -3627,35 +3594,35 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="3" t="s">
+      <c r="A198" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="B198" s="15" t="s">
+      <c r="B198" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
+      <c r="A199" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B199" t="s">
         <v>402</v>
-      </c>
-      <c r="B199" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B200" t="s">
         <v>404</v>
-      </c>
-      <c r="B200" s="16" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" t="s">
         <v>406</v>
-      </c>
-      <c r="B201" s="10" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
@@ -3667,7 +3634,7 @@
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="3" t="s">
         <v>409</v>
       </c>
       <c r="B203" t="s">
@@ -3675,124 +3642,84 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="11" t="s">
+      <c r="A204" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B204" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B204" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="3" t="s">
+      <c r="A205" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B205" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="B205" t="s">
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="14" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="10" t="s">
+      <c r="B206" t="s">
         <v>415</v>
       </c>
-      <c r="B206" t="s">
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B207" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B207" t="s">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="10" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="3" t="s">
+      <c r="B208" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B208" t="s">
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="14" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B209" s="10" t="s">
+      <c r="B209" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
-        <v>158</v>
+        <v>422</v>
       </c>
       <c r="B210" s="17" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="18" t="s">
+      <c r="A211" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="17" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="B212" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="B214" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="B215" s="17" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="B216" s="17" t="s">
-        <v>435</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C47" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
-    <hyperlink ref="C103" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
-    <hyperlink ref="C98" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
-    <hyperlink ref="C100" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
-    <hyperlink ref="C99" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
-    <hyperlink ref="C101" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
-    <hyperlink ref="C97" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
-    <hyperlink ref="B141" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
+    <hyperlink ref="C98" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
+    <hyperlink ref="C93" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
+    <hyperlink ref="C95" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
+    <hyperlink ref="C94" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
+    <hyperlink ref="C96" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
+    <hyperlink ref="C92" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
+    <hyperlink ref="B136" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
     <hyperlink ref="C49" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
-    <hyperlink ref="C137" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
-    <hyperlink ref="C135" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
-    <hyperlink ref="C136" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
+    <hyperlink ref="C132" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
+    <hyperlink ref="C130" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
+    <hyperlink ref="C131" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4BDE2-C2FB-400A-A9C9-767C3BFB4C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F992399-6436-4B84-AEA3-44815CB12708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2010" yWindow="2145" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="1620" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="414">
   <si>
     <t>티커</t>
   </si>
@@ -136,12 +136,6 @@
     <t>DB손해보험</t>
   </si>
   <si>
-    <t>000060</t>
-  </si>
-  <si>
-    <t>메리츠화재</t>
-  </si>
-  <si>
     <t>138040</t>
   </si>
   <si>
@@ -274,12 +268,6 @@
     <t>헥토파이낸셜</t>
   </si>
   <si>
-    <t>053580</t>
-  </si>
-  <si>
-    <t>웹케시</t>
-  </si>
-  <si>
     <t>211050</t>
   </si>
   <si>
@@ -322,12 +310,6 @@
     <t>한미반도체</t>
   </si>
   <si>
-    <t>005490</t>
-  </si>
-  <si>
-    <t>POSCO홀딩스</t>
-  </si>
-  <si>
     <t>000660</t>
   </si>
   <si>
@@ -430,12 +412,6 @@
     <t>한일시멘트</t>
   </si>
   <si>
-    <t>000990</t>
-  </si>
-  <si>
-    <t>DB하이텍</t>
-  </si>
-  <si>
     <t>053210</t>
   </si>
   <si>
@@ -658,12 +634,6 @@
     <t>풍산</t>
   </si>
   <si>
-    <t>010120</t>
-  </si>
-  <si>
-    <t>LS ELECTRIC</t>
-  </si>
-  <si>
     <t>329180</t>
   </si>
   <si>
@@ -734,12 +704,6 @@
   </si>
   <si>
     <t>한국석유</t>
-  </si>
-  <si>
-    <t>012510</t>
-  </si>
-  <si>
-    <t>더존비즈온</t>
   </si>
   <si>
     <t>267260</t>
@@ -1956,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -1971,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2325,6 +2289,9 @@
       <c r="B45" t="s">
         <v>89</v>
       </c>
+      <c r="C45" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -2333,6 +2300,9 @@
       <c r="B46" t="s">
         <v>91</v>
       </c>
+      <c r="C46" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -2342,7 +2312,7 @@
         <v>93</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2352,22 +2322,16 @@
       <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="C48" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>96</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -2375,7 +2339,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -2383,7 +2347,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -2391,7 +2355,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -2399,7 +2363,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -2407,7 +2371,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2415,7 +2379,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -2423,7 +2387,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -2431,7 +2395,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -2439,7 +2403,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -2447,7 +2411,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -2455,7 +2419,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -2463,7 +2427,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -2471,7 +2435,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -2479,7 +2443,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -2678,6 +2642,9 @@
       <c r="B88" t="s">
         <v>175</v>
       </c>
+      <c r="C88" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -2686,6 +2653,9 @@
       <c r="B89" t="s">
         <v>177</v>
       </c>
+      <c r="C89" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -2694,6 +2664,9 @@
       <c r="B90" t="s">
         <v>179</v>
       </c>
+      <c r="C90" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -2702,6 +2675,9 @@
       <c r="B91" t="s">
         <v>181</v>
       </c>
+      <c r="C91" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
@@ -2711,7 +2687,7 @@
         <v>183</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2721,9 +2697,6 @@
       <c r="B93" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -2733,7 +2706,7 @@
         <v>187</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -2743,9 +2716,6 @@
       <c r="B95" t="s">
         <v>189</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -2754,11 +2724,8 @@
       <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -2766,18 +2733,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>194</v>
       </c>
       <c r="B98" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -2785,7 +2749,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -2793,7 +2757,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -2801,7 +2765,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -2809,7 +2773,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -2817,7 +2781,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>206</v>
       </c>
@@ -2825,7 +2789,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -2833,7 +2797,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -2841,7 +2805,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -2849,7 +2813,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>214</v>
       </c>
@@ -2857,7 +2821,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -2865,7 +2829,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -2873,7 +2837,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>220</v>
       </c>
@@ -2881,7 +2845,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>222</v>
       </c>
@@ -2889,7 +2853,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>224</v>
       </c>
@@ -2897,7 +2861,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>226</v>
       </c>
@@ -2905,7 +2869,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -2913,7 +2877,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>230</v>
       </c>
@@ -2921,7 +2885,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -2929,7 +2893,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>234</v>
       </c>
@@ -2937,7 +2901,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>236</v>
       </c>
@@ -2945,7 +2909,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>238</v>
       </c>
@@ -2953,7 +2917,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -2961,7 +2925,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>242</v>
       </c>
@@ -2969,7 +2933,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -2977,139 +2941,139 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>246</v>
       </c>
       <c r="B124" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C124" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>248</v>
       </c>
       <c r="B125" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C125" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>250</v>
       </c>
       <c r="B126" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>252</v>
+      <c r="C126" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>254</v>
-      </c>
-      <c r="B128" t="s">
         <v>255</v>
       </c>
+      <c r="C127" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C128" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B129" t="s">
+        <v>260</v>
+      </c>
+      <c r="C129" t="s">
         <v>256</v>
       </c>
-      <c r="B129" t="s">
-        <v>257</v>
-      </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>258</v>
-      </c>
-      <c r="B130" t="s">
-        <v>259</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>275</v>
+      <c r="A130" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>260</v>
-      </c>
-      <c r="B131" t="s">
-        <v>261</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>275</v>
+      <c r="A131" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>262</v>
+      <c r="A132" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>263</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B133" t="s">
-        <v>267</v>
-      </c>
-      <c r="C133" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C134" t="s">
-        <v>268</v>
+        <v>271</v>
+      </c>
+      <c r="B134" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B135" t="s">
-        <v>272</v>
-      </c>
-      <c r="C135" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C136" t="s">
-        <v>268</v>
+        <v>275</v>
+      </c>
+      <c r="B136" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C137" s="3" t="s">
+      <c r="B137" t="s">
         <v>278</v>
       </c>
     </row>
@@ -3130,7 +3094,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="3" t="s">
         <v>283</v>
       </c>
       <c r="B140" t="s">
@@ -3226,7 +3190,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="A152" s="4" t="s">
         <v>307</v>
       </c>
       <c r="B152" t="s">
@@ -3234,7 +3198,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="4" t="s">
         <v>309</v>
       </c>
       <c r="B153" t="s">
@@ -3274,7 +3238,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="3" t="s">
         <v>319</v>
       </c>
       <c r="B158" t="s">
@@ -3282,7 +3246,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="3" t="s">
         <v>321</v>
       </c>
       <c r="B159" t="s">
@@ -3322,18 +3286,18 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+      <c r="A164" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B164" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B164" t="s">
-        <v>332</v>
-      </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="9" t="s">
         <v>334</v>
       </c>
     </row>
@@ -3346,7 +3310,7 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="A167" s="10" t="s">
         <v>337</v>
       </c>
       <c r="B167" t="s">
@@ -3357,31 +3321,31 @@
       <c r="A168" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="10" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="A169" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B169" t="s">
         <v>341</v>
       </c>
-      <c r="B169" t="s">
-        <v>342</v>
-      </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="7" t="s">
+      <c r="A170" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B170" t="s">
         <v>344</v>
       </c>
-      <c r="B170" s="6" t="s">
-        <v>343</v>
-      </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B171" t="s">
         <v>346</v>
       </c>
     </row>
@@ -3389,8 +3353,8 @@
       <c r="A172" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B172" t="s">
-        <v>348</v>
+      <c r="B172" s="10" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -3402,23 +3366,23 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
+      <c r="A174" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B174" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B175" t="s">
+      <c r="A175" s="10" t="s">
         <v>353</v>
       </c>
+      <c r="B175" s="10" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+      <c r="A176" s="10" t="s">
         <v>355</v>
       </c>
       <c r="B176" t="s">
@@ -3426,31 +3390,31 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="10" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
+      <c r="A178" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B178" s="10" t="s">
-        <v>354</v>
+      <c r="B178" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="13" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="10" t="s">
+      <c r="A180" s="11" t="s">
         <v>363</v>
       </c>
       <c r="B180" t="s">
@@ -3458,15 +3422,15 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="10" t="s">
+      <c r="A181" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B181" s="10" t="s">
+      <c r="B181" s="15" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="10" t="s">
+      <c r="A182" s="3" t="s">
         <v>367</v>
       </c>
       <c r="B182" t="s">
@@ -3477,12 +3441,12 @@
       <c r="A183" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B183" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="3" t="s">
         <v>371</v>
       </c>
       <c r="B184" t="s">
@@ -3490,15 +3454,15 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="10" t="s">
+      <c r="A185" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="3" t="s">
         <v>375</v>
       </c>
       <c r="B186" t="s">
@@ -3506,7 +3470,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="14" t="s">
+      <c r="A187" s="3" t="s">
         <v>377</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -3515,38 +3479,38 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B188" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B190" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B188" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="B189" s="15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B190" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="11" t="s">
+      <c r="A191" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="15" t="s">
+      <c r="B191" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="3" t="s">
+      <c r="A192" s="11" t="s">
         <v>387</v>
       </c>
       <c r="B192" t="s">
@@ -3554,35 +3518,35 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="3" t="s">
+      <c r="A193" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="B193" s="15" t="s">
+      <c r="B193" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B194" t="s">
         <v>392</v>
       </c>
-      <c r="B194" t="s">
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="10" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
+      <c r="B195" t="s">
         <v>394</v>
       </c>
-      <c r="B195" s="16" t="s">
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="10" t="s">
+      <c r="B196" t="s">
         <v>396</v>
-      </c>
-      <c r="B196" s="10" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
@@ -3594,27 +3558,27 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="11" t="s">
+      <c r="A198" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B198" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B198" t="s">
-        <v>400</v>
-      </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="11" t="s">
+      <c r="A199" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B199" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="B199" t="s">
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="14" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="3" t="s">
+      <c r="B200" t="s">
         <v>403</v>
-      </c>
-      <c r="B200" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
@@ -3622,104 +3586,56 @@
         <v>405</v>
       </c>
       <c r="B201" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="10" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="3" t="s">
+      <c r="B202" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B202" t="s">
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="14" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="3" t="s">
+      <c r="B203" t="s">
         <v>409</v>
-      </c>
-      <c r="B203" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="B204" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B204" s="17" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
-        <v>148</v>
+        <v>412</v>
       </c>
       <c r="B205" s="17" t="s">
         <v>413</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="B206" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="B207" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="B209" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B210" s="17" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="B211" s="17" t="s">
-        <v>425</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C47" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
-    <hyperlink ref="C98" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
-    <hyperlink ref="C93" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
-    <hyperlink ref="C95" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
-    <hyperlink ref="C94" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
-    <hyperlink ref="C96" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
-    <hyperlink ref="C92" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
-    <hyperlink ref="B136" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
-    <hyperlink ref="C49" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
-    <hyperlink ref="C132" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
-    <hyperlink ref="C130" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
-    <hyperlink ref="C131" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
+    <hyperlink ref="C45" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
+    <hyperlink ref="C94" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
+    <hyperlink ref="C89" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
+    <hyperlink ref="C91" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
+    <hyperlink ref="C90" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
+    <hyperlink ref="C92" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
+    <hyperlink ref="C88" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
+    <hyperlink ref="B130" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
+    <hyperlink ref="C47" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
+    <hyperlink ref="C126" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
+    <hyperlink ref="C124" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
+    <hyperlink ref="C125" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>

--- a/api/대상티커.xlsx
+++ b/api/대상티커.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F992399-6436-4B84-AEA3-44815CB12708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC2AD9B-BB0A-4241-B6C5-9F2663A7E9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="1620" windowWidth="23865" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="412">
   <si>
     <t>티커</t>
   </si>
@@ -182,12 +182,6 @@
   </si>
   <si>
     <t>한국캐피탈</t>
-  </si>
-  <si>
-    <t>008110</t>
-  </si>
-  <si>
-    <t>대동전자</t>
   </si>
   <si>
     <t>003540</t>
@@ -1920,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C204"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
@@ -1935,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2281,6 +2275,9 @@
       <c r="B44" t="s">
         <v>87</v>
       </c>
+      <c r="C44" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -2289,8 +2286,8 @@
       <c r="B45" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>253</v>
+      <c r="C45" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -2300,8 +2297,8 @@
       <c r="B46" t="s">
         <v>91</v>
       </c>
-      <c r="C46" t="s">
-        <v>263</v>
+      <c r="C46" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -2311,9 +2308,6 @@
       <c r="B47" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -2634,6 +2628,9 @@
       <c r="B87" t="s">
         <v>173</v>
       </c>
+      <c r="C87" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -2643,7 +2640,7 @@
         <v>175</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -2654,7 +2651,7 @@
         <v>177</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -2665,7 +2662,7 @@
         <v>179</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -2676,7 +2673,7 @@
         <v>181</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -2686,9 +2683,6 @@
       <c r="B92" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
@@ -2697,6 +2691,9 @@
       <c r="B93" t="s">
         <v>185</v>
       </c>
+      <c r="C93" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -2705,9 +2702,6 @@
       <c r="B94" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -2940,6 +2934,9 @@
       <c r="B123" t="s">
         <v>245</v>
       </c>
+      <c r="C123" s="2" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -2949,7 +2946,7 @@
         <v>247</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -2960,72 +2957,69 @@
         <v>249</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>250</v>
+      <c r="A126" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="B126" t="s">
-        <v>251</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="C126" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C127" t="s">
         <v>254</v>
       </c>
-      <c r="B127" t="s">
-        <v>255</v>
-      </c>
-      <c r="C127" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" t="s">
         <v>258</v>
       </c>
       <c r="C128" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B129" t="s">
-        <v>260</v>
-      </c>
       <c r="C129" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C130" t="s">
-        <v>256</v>
+      <c r="C130" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C131" s="3" t="s">
+      <c r="B131" t="s">
         <v>266</v>
       </c>
     </row>
@@ -3038,7 +3032,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="4" t="s">
         <v>269</v>
       </c>
       <c r="B133" t="s">
@@ -3046,7 +3040,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B134" t="s">
@@ -3182,7 +3176,7 @@
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="A151" s="4" t="s">
         <v>305</v>
       </c>
       <c r="B151" t="s">
@@ -3198,7 +3192,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="3" t="s">
         <v>309</v>
       </c>
       <c r="B153" t="s">
@@ -3278,31 +3272,31 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
+      <c r="A163" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B163" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="B163" t="s">
-        <v>330</v>
-      </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B164" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B164" s="6" t="s">
-        <v>331</v>
-      </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B165" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+      <c r="A166" s="10" t="s">
         <v>335</v>
       </c>
       <c r="B166" t="s">
@@ -3310,31 +3304,31 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="10" t="s">
+      <c r="A167" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="10" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="A168" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B168" t="s">
         <v>339</v>
       </c>
-      <c r="B168" s="10" t="s">
-        <v>340</v>
-      </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="11" t="s">
-        <v>348</v>
+      <c r="A169" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="B169" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="A170" s="11" t="s">
         <v>343</v>
       </c>
       <c r="B170" t="s">
@@ -3342,19 +3336,19 @@
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B171" t="s">
-        <v>346</v>
+      <c r="B171" s="10" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
+      <c r="A172" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="B172" s="10" t="s">
-        <v>342</v>
+      <c r="B172" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -3369,7 +3363,7 @@
       <c r="A174" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="10" t="s">
         <v>352</v>
       </c>
     </row>
@@ -3377,7 +3371,7 @@
       <c r="A175" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B175" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3385,79 +3379,79 @@
       <c r="A176" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="10" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="10" t="s">
+      <c r="A177" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B177" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="12" t="s">
+      <c r="A178" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="13" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="10" t="s">
+      <c r="A179" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="15" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="14" t="s">
+      <c r="A181" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B181" s="15" t="s">
+      <c r="B181" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
+      <c r="A182" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="15" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="10" t="s">
+      <c r="A183" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B183" s="15" t="s">
+      <c r="B183" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
+      <c r="A184" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="15" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="11" t="s">
+      <c r="A185" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B185" s="15" t="s">
+      <c r="B185" t="s">
         <v>374</v>
       </c>
     </row>
@@ -3465,44 +3459,44 @@
       <c r="A186" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B187" s="15" t="s">
         <v>378</v>
+      </c>
+      <c r="B187" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="16" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
+      <c r="A189" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B189" s="16" t="s">
+      <c r="B189" s="10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="10" t="s">
+      <c r="B190" t="s">
         <v>384</v>
       </c>
-      <c r="B190" s="10" t="s">
-        <v>379</v>
-      </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="3" t="s">
+      <c r="A191" s="11" t="s">
         <v>385</v>
       </c>
       <c r="B191" t="s">
@@ -3518,7 +3512,7 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="11" t="s">
+      <c r="A193" s="3" t="s">
         <v>389</v>
       </c>
       <c r="B193" t="s">
@@ -3526,7 +3520,7 @@
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="3" t="s">
+      <c r="A194" s="10" t="s">
         <v>391</v>
       </c>
       <c r="B194" t="s">
@@ -3534,7 +3528,7 @@
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="10" t="s">
+      <c r="A195" s="3" t="s">
         <v>393</v>
       </c>
       <c r="B195" t="s">
@@ -3550,58 +3544,58 @@
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
+      <c r="A197" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B197" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="B197" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B198" s="17" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="B198" s="10" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B199" s="17" t="s">
+      <c r="B199" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="14" t="s">
+      <c r="A200" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B200" t="s">
         <v>402</v>
-      </c>
-      <c r="B200" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B201" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B201" t="s">
-        <v>404</v>
-      </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="10" t="s">
+      <c r="A202" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B202" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="14" t="s">
+      <c r="A203" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="17" t="s">
         <v>409</v>
       </c>
     </row>
@@ -3613,29 +3607,21 @@
         <v>411</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="B205" s="17" t="s">
-        <v>413</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C45" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
-    <hyperlink ref="C94" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
-    <hyperlink ref="C89" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
-    <hyperlink ref="C91" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
-    <hyperlink ref="C90" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
-    <hyperlink ref="C92" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
-    <hyperlink ref="C88" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
-    <hyperlink ref="B130" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
-    <hyperlink ref="C47" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
-    <hyperlink ref="C126" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
-    <hyperlink ref="C124" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
-    <hyperlink ref="C125" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
+    <hyperlink ref="C44" r:id="rId1" display="javascript:void(0)" xr:uid="{C5FD1DD4-CBE5-4177-A060-03411BF4DDD8}"/>
+    <hyperlink ref="C93" r:id="rId2" display="javascript:void(0)" xr:uid="{F17E69A7-3064-48E2-8E63-AED4AC88A599}"/>
+    <hyperlink ref="C88" r:id="rId3" display="javascript:void(0)" xr:uid="{66345BF0-536C-4DC7-A764-488D21621269}"/>
+    <hyperlink ref="C90" r:id="rId4" display="javascript:void(0)" xr:uid="{BDFE1FDE-6CA9-4FF2-825E-643E5C304387}"/>
+    <hyperlink ref="C89" r:id="rId5" display="javascript:void(0)" xr:uid="{687820A8-A4CE-4BBC-8A72-33C02E08981E}"/>
+    <hyperlink ref="C91" r:id="rId6" display="javascript:void(0)" xr:uid="{D33C0EE2-FC32-4FED-A4C9-F96E3CD755B6}"/>
+    <hyperlink ref="C87" r:id="rId7" display="javascript:void(0)" xr:uid="{EBC80AEC-F2B0-4E32-A641-C5A50745E0FF}"/>
+    <hyperlink ref="B129" r:id="rId8" display="https://finance.daum.net/quotes/A015360" xr:uid="{8E636016-75E4-4B30-BDB2-9A259E1464EF}"/>
+    <hyperlink ref="C46" r:id="rId9" display="javascript:void(0)" xr:uid="{8BBBF6FA-5C91-4B1B-B253-8E8B706A1C2E}"/>
+    <hyperlink ref="C125" r:id="rId10" display="javascript:void(0)" xr:uid="{D1998EF3-E8E4-4511-80C7-DD5571D48609}"/>
+    <hyperlink ref="C123" r:id="rId11" display="javascript:void(0)" xr:uid="{57CD9445-584B-408A-8514-9F4E07CA4FA7}"/>
+    <hyperlink ref="C124" r:id="rId12" display="javascript:void(0)" xr:uid="{C7232A73-D80F-413C-B169-CE84648FBCD5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
